--- a/data/trans_camb/IP1003-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 3,21</t>
+          <t>-8,21; 3,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,07; -1,32</t>
+          <t>-11,49; -1,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 3,44</t>
+          <t>-8,46; 3,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 8,49</t>
+          <t>-3,25; 8,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 11,85</t>
+          <t>-2,88; 11,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 17,48</t>
+          <t>-0,67; 16,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 4,45</t>
+          <t>-3,83; 4,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 3,66</t>
+          <t>-4,99; 3,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 8,28</t>
+          <t>-3,26; 8,76</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-76,27; 98,33</t>
+          <t>-80,44; 103,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 15,41</t>
+          <t>-100,0; 66,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-90,97; 103,01</t>
+          <t>-87,33; 118,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,91; 388,28</t>
+          <t>-49,95; 420,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,12; 502,72</t>
+          <t>-48,24; 479,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,45; 647,36</t>
+          <t>-22,47; 864,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,53; 111,87</t>
+          <t>-50,8; 112,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,01; 92,53</t>
+          <t>-66,82; 90,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-46,34; 214,43</t>
+          <t>-45,12; 197,74</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,86</t>
+          <t>-3,63; 1,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,8</t>
+          <t>-3,36; 1,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 2,99</t>
+          <t>-2,3; 2,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,43</t>
+          <t>-4,07; 1,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,55</t>
+          <t>-4,39; 0,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 3,53</t>
+          <t>-2,26; 3,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 0,76</t>
+          <t>-2,93; 0,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,44</t>
+          <t>-3,22; 0,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,35</t>
+          <t>-1,7; 2,29</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,3; 42,53</t>
+          <t>-51,01; 36,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 43,37</t>
+          <t>-45,45; 36,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 68,79</t>
+          <t>-33,28; 65,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,51; 26,11</t>
+          <t>-47,08; 27,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,17; 8,22</t>
+          <t>-51,7; 13,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 56,81</t>
+          <t>-26,54; 62,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,2; 14,6</t>
+          <t>-38,57; 13,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 8,58</t>
+          <t>-42,36; 8,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,05; 39,57</t>
+          <t>-22,93; 38,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 2,04</t>
+          <t>-5,59; 2,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 2,56</t>
+          <t>-5,67; 2,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 3,31</t>
+          <t>-4,95; 4,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 2,96</t>
+          <t>-5,48; 3,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 0,09</t>
+          <t>-7,43; 0,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 6,98</t>
+          <t>-3,13; 6,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 1,58</t>
+          <t>-4,2; 1,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 0,19</t>
+          <t>-5,26; 0,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 4,38</t>
+          <t>-2,65; 4,34</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,9; 56,5</t>
+          <t>-69,29; 71,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-66,95; 64,94</t>
+          <t>-68,04; 77,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-63,67; 83,71</t>
+          <t>-61,31; 122,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-64,19; 77,73</t>
+          <t>-62,18; 75,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-80,75; 17,19</t>
+          <t>-84,44; 3,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,91; 179,05</t>
+          <t>-38,25; 159,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,29; 34,09</t>
+          <t>-55,68; 38,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,06; 4,16</t>
+          <t>-65,72; 10,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-35,14; 94,86</t>
+          <t>-34,32; 86,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,77</t>
+          <t>-3,34; 0,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,41</t>
+          <t>-3,31; 0,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,67</t>
+          <t>-2,46; 1,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1,39</t>
+          <t>-3,0; 1,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,45</t>
+          <t>-3,79; 0,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,95</t>
+          <t>-1,32; 3,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,54</t>
+          <t>-2,49; 0,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; -0,11</t>
+          <t>-2,99; -0,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,25</t>
+          <t>-1,22; 2,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 16,19</t>
+          <t>-47,17; 11,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 9,86</t>
+          <t>-47,9; 16,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,57; 34,86</t>
+          <t>-36,57; 32,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 23,59</t>
+          <t>-37,17; 19,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,16; 7,78</t>
+          <t>-46,91; 5,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 68,52</t>
+          <t>-17,49; 66,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 10,33</t>
+          <t>-34,45; 8,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-41,82; -1,02</t>
+          <t>-42,02; -2,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 37,94</t>
+          <t>-16,98; 35,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1003-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 3,74</t>
+          <t>-8,22; 3,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,49; -1,96</t>
+          <t>-10,67; -1,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 3,63</t>
+          <t>-8,73; 4,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 8,95</t>
+          <t>-3,75; 9,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 11,33</t>
+          <t>-2,64; 11,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 16,9</t>
+          <t>-1,08; 16,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 4,66</t>
+          <t>-4,22; 4,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 3,67</t>
+          <t>-5,09; 3,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 8,76</t>
+          <t>-3,44; 9,89</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-80,44; 103,14</t>
+          <t>-82,1; 110,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,3</t>
+          <t>-100,0; 43,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-87,33; 118,82</t>
+          <t>-88,79; 130,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,95; 420,03</t>
+          <t>-56,72; 439,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,24; 479,27</t>
+          <t>-50,25; 606,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 864,4</t>
+          <t>-33,45; 676,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,8; 112,05</t>
+          <t>-52,14; 101,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,82; 90,57</t>
+          <t>-65,45; 83,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,12; 197,74</t>
+          <t>-49,86; 210,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 1,56</t>
+          <t>-3,27; 1,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,63</t>
+          <t>-2,98; 1,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 2,93</t>
+          <t>-2,52; 2,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 1,66</t>
+          <t>-3,7; 1,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,77</t>
+          <t>-4,41; 0,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,71</t>
+          <t>-2,23; 3,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,8</t>
+          <t>-2,88; 0,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,48</t>
+          <t>-3,13; 0,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,29</t>
+          <t>-1,59; 2,61</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,01; 36,21</t>
+          <t>-47,37; 37,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-45,45; 36,75</t>
+          <t>-43,18; 43,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 65,9</t>
+          <t>-37,11; 62,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,08; 27,78</t>
+          <t>-43,26; 25,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,7; 13,38</t>
+          <t>-51,41; 13,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 62,12</t>
+          <t>-25,91; 58,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,57; 13,74</t>
+          <t>-38,07; 14,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,36; 8,91</t>
+          <t>-41,93; 7,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 38,87</t>
+          <t>-21,43; 46,81</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 2,63</t>
+          <t>-5,77; 2,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 2,83</t>
+          <t>-5,61; 2,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 4,2</t>
+          <t>-4,93; 3,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 3,12</t>
+          <t>-5,72; 2,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 0,11</t>
+          <t>-7,65; 0,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 6,67</t>
+          <t>-3,08; 6,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,7</t>
+          <t>-4,43; 1,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 0,09</t>
+          <t>-5,65; 0,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 4,34</t>
+          <t>-2,82; 3,92</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,29; 71,81</t>
+          <t>-71,07; 61,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-68,04; 77,86</t>
+          <t>-67,65; 53,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,31; 122,22</t>
+          <t>-63,3; 87,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,18; 75,31</t>
+          <t>-63,32; 66,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-84,44; 3,58</t>
+          <t>-83,49; 7,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 159,2</t>
+          <t>-37,14; 154,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,68; 38,27</t>
+          <t>-55,6; 31,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,72; 10,58</t>
+          <t>-69,04; 6,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 86,01</t>
+          <t>-35,41; 80,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,53</t>
+          <t>-3,36; 0,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,79</t>
+          <t>-3,49; 0,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,73</t>
+          <t>-2,62; 1,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 1,13</t>
+          <t>-3,17; 1,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 0,16</t>
+          <t>-3,81; 0,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,89</t>
+          <t>-1,28; 3,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,47</t>
+          <t>-2,47; 0,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; -0,15</t>
+          <t>-3,03; -0,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,08</t>
+          <t>-1,18; 2,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,17; 11,26</t>
+          <t>-46,6; 16,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,9; 16,58</t>
+          <t>-49,28; 11,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 32,78</t>
+          <t>-37,59; 35,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 19,33</t>
+          <t>-38,59; 23,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,91; 5,66</t>
+          <t>-47,44; 8,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 66,06</t>
+          <t>-16,46; 63,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,45; 8,13</t>
+          <t>-35,0; 5,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,02; -2,82</t>
+          <t>-42,18; -4,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 35,91</t>
+          <t>-17,26; 35,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1003-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,53</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,35</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,39</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-5,91</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,07</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,53</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,35</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,3</t>
+          <t>-2,16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>2,41</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 3,49</t>
+          <t>-3,73; 8,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -1,3</t>
+          <t>-3,14; 11,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 4,12</t>
+          <t>-1,82; 17,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 9,58</t>
+          <t>-7,48; 3,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 11,25</t>
+          <t>-11,07; -1,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 16,57</t>
+          <t>-8,46; 4,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 4,3</t>
+          <t>-4,05; 4,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 3,21</t>
+          <t>-5,23; 3,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 9,89</t>
+          <t>-3,12; 9,27</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>50,33%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>66,69%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>127,06%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-31,95%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-84,08%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-43,68%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>50,33%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>66,69%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>125,21%</t>
+          <t>-30,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-82,1; 110,24</t>
+          <t>-50,91; 388,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 43,74</t>
+          <t>-47,12; 502,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-88,79; 130,33</t>
+          <t>-38,51; 675,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-56,72; 439,7</t>
+          <t>-76,27; 98,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,25; 606,26</t>
+          <t>-100,0; 15,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,45; 676,99</t>
+          <t>-87,71; 159,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,14; 101,85</t>
+          <t>-50,53; 111,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,45; 83,55</t>
+          <t>-70,01; 92,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,86; 210,95</t>
+          <t>-44,45; 221,1</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,85</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,48</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,71</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,25</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,85</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,58</t>
+          <t>-3,64; 1,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,83</t>
+          <t>-4,65; 0,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,81</t>
+          <t>-2,58; 3,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 1,48</t>
+          <t>-3,08; 1,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,91</t>
+          <t>-3,21; 1,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,58</t>
+          <t>-1,67; 3,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,81</t>
+          <t>-2,76; 0,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 0,45</t>
+          <t>-3,21; 0,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,61</t>
+          <t>-1,36; 2,68</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-16,96%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-25,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-14,88%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-12,5%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-16,96%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-25,0%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,37; 37,09</t>
+          <t>-44,51; 26,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,18; 43,07</t>
+          <t>-55,17; 8,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 62,84</t>
+          <t>-31,72; 51,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,26; 25,09</t>
+          <t>-46,3; 42,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,41; 13,82</t>
+          <t>-47,68; 43,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 58,84</t>
+          <t>-24,66; 89,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,07; 14,75</t>
+          <t>-37,2; 14,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 7,32</t>
+          <t>-41,22; 8,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 46,81</t>
+          <t>-17,89; 46,79</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,22</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,48</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,17</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,82</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,47</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,22</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,48</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,85</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 2,18</t>
+          <t>-5,96; 2,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 2,35</t>
+          <t>-7,68; 0,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 3,33</t>
+          <t>-2,99; 7,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 2,69</t>
+          <t>-5,72; 2,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 0,24</t>
+          <t>-5,47; 2,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 6,77</t>
+          <t>-4,81; 3,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,39</t>
+          <t>-4,35; 1,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 0,01</t>
+          <t>-5,14; 0,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 3,92</t>
+          <t>-2,35; 4,82</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-18,64%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-53,01%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33,09%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-29,46%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-23,84%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-16,88%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-18,64%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-53,01%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>-11,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-71,07; 61,93</t>
+          <t>-64,19; 77,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,65; 53,04</t>
+          <t>-80,75; 17,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-63,3; 87,57</t>
+          <t>-35,88; 193,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,32; 66,91</t>
+          <t>-70,9; 56,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,49; 7,95</t>
+          <t>-66,95; 64,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,14; 154,9</t>
+          <t>-60,86; 97,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,6; 31,68</t>
+          <t>-55,29; 34,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,04; 6,59</t>
+          <t>-66,06; 4,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 80,47</t>
+          <t>-30,9; 100,46</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,81</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,74</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,44</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,41</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,74</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,75</t>
+          <t>-3,05; 1,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,59</t>
+          <t>-3,8; 0,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,74</t>
+          <t>-0,98; 3,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,35</t>
+          <t>-3,24; 0,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,4</t>
+          <t>-3,52; 0,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,83</t>
+          <t>-2,09; 2,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,33</t>
+          <t>-2,46; 0,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; -0,28</t>
+          <t>-3,02; -0,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,08</t>
+          <t>-0,8; 2,71</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-11,72%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-25,12%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20,83%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-21,26%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-23,55%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-7,41%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-11,72%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-25,12%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,6; 16,39</t>
+          <t>-37,67; 23,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,28; 11,42</t>
+          <t>-47,16; 7,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,59; 35,0</t>
+          <t>-12,14; 68,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,59; 23,36</t>
+          <t>-46,57; 16,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,44; 8,33</t>
+          <t>-49,62; 9,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 63,62</t>
+          <t>-29,35; 49,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 5,93</t>
+          <t>-34,43; 10,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,18; -4,07</t>
+          <t>-41,82; -1,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 35,61</t>
+          <t>-11,06; 46,39</t>
         </is>
       </c>
     </row>
